--- a/Intro a ALM.xlsx
+++ b/Intro a ALM.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\TRABAJO\UNI\8VO SEMESTRE\ADMINISTRACION_RIESGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10D5280-597C-450F-A92E-93EBD496B9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA4DBC7-7075-41DD-ACAC-BF80C26D3B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1682C8E6-3557-4F1A-9CCD-D66807DB5FB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1682C8E6-3557-4F1A-9CCD-D66807DB5FB0}"/>
   </bookViews>
   <sheets>
     <sheet name="balance" sheetId="1" r:id="rId1"/>
     <sheet name="resultados" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -400,6 +403,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="baance"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -720,16 +736,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3C70B2-8E9A-4FA8-9E8E-DD28E654A893}">
   <dimension ref="B2:L25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
@@ -743,7 +759,7 @@
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -757,7 +773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -786,7 +802,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -815,7 +831,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -834,7 +850,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
@@ -854,7 +870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
@@ -880,7 +896,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
@@ -906,7 +922,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
@@ -920,11 +936,11 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
@@ -954,7 +970,7 @@
         <v>7300</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
         <v>2</v>
       </c>
@@ -968,7 +984,7 @@
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>3</v>
       </c>
@@ -982,7 +998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1008,7 +1024,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
@@ -1034,7 +1050,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
@@ -1056,7 +1072,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
@@ -1082,7 +1098,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
@@ -1102,7 +1118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
@@ -1128,7 +1144,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
@@ -1154,11 +1170,11 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>13</v>
       </c>
@@ -1202,12 +1218,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED35D34-3155-490B-B267-86580FD3653D}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
@@ -1221,12 +1237,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -1253,16 +1269,16 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="C4">
-        <f>A4*balance!C5</f>
-        <v>32.5</v>
+      <c r="C4" t="e">
+        <f>A4*[1]baance!C5</f>
+        <v>#REF!</v>
       </c>
       <c r="D4">
         <f>A4*balance!H5</f>
@@ -1280,7 +1296,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>0.48</v>
       </c>
@@ -1304,7 +1320,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>0.24</v>
       </c>
@@ -1331,7 +1347,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>0.1</v>
       </c>
@@ -1357,7 +1373,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>0.16</v>
       </c>
@@ -1381,7 +1397,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>0.11</v>
       </c>
@@ -1405,14 +1421,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="9" t="e">
         <f>SUM(C3:C8)</f>
-        <v>1217.5</v>
+        <v>#REF!</v>
       </c>
       <c r="D10" s="9">
         <f t="shared" ref="D10:F10" si="0">SUM(D3:D8)</f>
@@ -1427,12 +1443,12 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>0</v>
       </c>
@@ -1456,7 +1472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>0.05</v>
       </c>
@@ -1480,7 +1496,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>6.9000000000000006E-2</v>
       </c>
@@ -1503,7 +1519,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>0.09</v>
       </c>
@@ -1528,7 +1544,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>41</v>
       </c>
@@ -1549,18 +1565,18 @@
         <v>272.60000000000002</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="10" t="e">
         <f>C10-C17</f>
-        <v>1142.5</v>
+        <v>#REF!</v>
       </c>
       <c r="D19" s="10">
         <f>D10-D17</f>
@@ -1578,13 +1594,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="12" t="e">
         <f>C19/(balance!E8+balance!E9)</f>
-        <v>0.95208333333333328</v>
+        <v>#REF!</v>
       </c>
       <c r="D20" s="12">
         <f>D19/(balance!J8+balance!J9)</f>
@@ -1599,7 +1615,7 @@
         <v>0.54381818181818187</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H23" t="s">
         <v>53</v>
       </c>
